--- a/JsonConverter/ExcelFiles/OO_DialogueGroup.xlsx
+++ b/JsonConverter/ExcelFiles/OO_DialogueGroup.xlsx
@@ -6,7 +6,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12770" yWindow="2240" windowWidth="19820" windowHeight="18420" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_Character&lt;Hero&gt;" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DNTable_DialogueGroup" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -78,8 +78,11 @@
       <sz val="10"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -120,6 +123,21 @@
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -165,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -194,6 +212,24 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -476,136 +512,137 @@
   <dimension ref="A1:O35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.54296875" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="19.453125" customWidth="1" style="3" min="1" max="1"/>
-    <col width="19.54296875" customWidth="1" style="3" min="2" max="2"/>
-    <col width="50.7265625" customWidth="1" style="3" min="3" max="3"/>
-    <col width="20.26953125" customWidth="1" style="3" min="4" max="4"/>
-    <col width="30.54296875" customWidth="1" style="3" min="5" max="5"/>
-    <col width="26.54296875" customWidth="1" style="3" min="6" max="6"/>
-    <col width="12.54296875" customWidth="1" style="3" min="7" max="16384"/>
+    <col width="17" customWidth="1" style="3" min="1" max="1"/>
+    <col width="14" customWidth="1" style="3" min="2" max="2"/>
+    <col width="14" customWidth="1" style="3" min="3" max="3"/>
+    <col width="29" customWidth="1" style="3" min="4" max="4"/>
+    <col width="23" customWidth="1" style="3" min="5" max="5"/>
+    <col width="14" customWidth="1" style="3" min="6" max="6"/>
+    <col width="26" customWidth="1" style="3" min="7" max="16384"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Dialogue group id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Group name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Group description</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Speaker character ids separated by |</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Fallback speaker names separated by |</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Shared dialogue text</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Dialogue ids separated by |</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Next dialogue group id</t>
+      <c r="A1" s="17" t="inlineStr">
+        <is>
+          <t>동시 대사 그룹 ID</t>
+        </is>
+      </c>
+      <c r="B1" s="17" t="inlineStr">
+        <is>
+          <t>그룹 이름</t>
+        </is>
+      </c>
+      <c r="C1" s="17" t="inlineStr">
+        <is>
+          <t>그룹 설명</t>
+        </is>
+      </c>
+      <c r="D1" s="17" t="inlineStr">
+        <is>
+          <t>동시에 말하는 캐릭터 ID 목록(| 구분)</t>
+        </is>
+      </c>
+      <c r="E1" s="17" t="inlineStr">
+        <is>
+          <t>대체 화자 이름 목록(| 구분)</t>
+        </is>
+      </c>
+      <c r="F1" s="18" t="inlineStr">
+        <is>
+          <t>공통 대사 내용</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
+          <t>기존 단일 대사 ID 목록(| 구분)</t>
+        </is>
+      </c>
+      <c r="H1" s="18" t="inlineStr">
+        <is>
+          <t>다음 대사 그룹 ID</t>
         </is>
       </c>
     </row>
     <row r="2" ht="13" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="19" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="E2" s="19" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="19" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="20" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="20" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="3" ht="15.75" customFormat="1" customHeight="1" s="13">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="21" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t>SpeakerCharacterIdList</t>
         </is>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="21" t="inlineStr">
         <is>
           <t>SpeakerNameList</t>
         </is>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t>DialogueIdList</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="22" t="inlineStr">
         <is>
           <t>NextDialogueGroupId</t>
         </is>

--- a/JsonConverter/ExcelFiles/OO_DialogueGroup.xlsx
+++ b/JsonConverter/ExcelFiles/OO_DialogueGroup.xlsx
@@ -656,12 +656,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>첫 채소죽 완성 합창</t>
+          <t>? ??? ?? ??</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>채소죽을 완성한 뒤 춘양, 재익군, 모란이 함께 감사 인사를 하는 대화 그룹.</t>
+          <t>???? ??? ? ??, ???, ??? ?? ?? ??? ?? ?? ??.</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">

--- a/JsonConverter/ExcelFiles/OO_DialogueGroup.xlsx
+++ b/JsonConverter/ExcelFiles/OO_DialogueGroup.xlsx
@@ -656,12 +656,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>? ??? ?? ??</t>
+          <t>야채죽 완성 감사 인사</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>???? ??? ? ??, ???, ??? ?? ?? ??? ?? ?? ??.</t>
+          <t>야채죽 완성 후 춘양, 재익군, 모란이 함께 감사 인사를 하는 동시 대사입니다.</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
